--- a/Audit_Report_DB.xlsx
+++ b/Audit_Report_DB.xlsx
@@ -1,25 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Documents_Pattamaporn\Desktop\DB\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18600" windowHeight="6860"/>
-  </bookViews>
   <sheets>
-    <sheet name="Database_TUV" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Database_TUV" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="ReportData" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="AdminList" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>Timestamp</t>
   </si>
@@ -89,38 +83,128 @@
   <si>
     <t>Yokoten_Files</t>
   </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>TUV-260518-083628</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>pppo</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1rrfDro83x-0bK5eP_du5tdK2iHTimwXO/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>nc1 (Major NC)</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>pppp</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1PciCFG9mSLv120qUBn65MkTnoOH7U5Pt/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>ppip</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1Rcj-YqQZ1ASgJ2_9uxpgypiuBfPeE3dS/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>isotraining99@gmail.com</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1VXMaR6OU6ovhak41Vynv1kTSp3mavyKR/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>TUV-260518-084124</t>
+  </si>
+  <si>
+    <t>rerte</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1-3W_tK9zyEvONUnO0wJVIs8qhOr0FYUk/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>OFI HMM</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>terteret</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1MCQ4CrTDgi3MjfjA4uEbjvo1Litoc-Nh/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>retrrette</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1l2XHqjl0NMX_114e63PC0563dHWZFyie/edit?usp=drivesdk&amp;ouid=105318077892435970535&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>user.a@minebea.co.th</t>
+  </si>
+  <si>
+    <t>TUV-260518-095634</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;ppp[9oi[o&lt;/p&gt;
+&lt;p&gt;&lt;a class="file-link-box file-excel" contenteditable="false" href="https://docs.google.com/spreadsheets/d/1B2hmB16w7S1zYeJdHoBfIOU93GHB-iAy/edit?usp=drivesdk&amp;amp;ouid=105318077892435970535&amp;amp;rtpof=true&amp;amp;sd=true" target="_blank" rel="noopener"&gt;📗 Information list MCN.xlsx&lt;/a&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="2">
-    <numFmt numFmtId="187" formatCode="m/d/yyyy\ h:mm:ss"/>
-    <numFmt numFmtId="188" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -128,7 +212,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -138,47 +222,54 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -186,7 +277,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -376,28 +467,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="7" max="7" width="13.26953125" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" customWidth="1"/>
-    <col min="9" max="9" width="16.26953125" customWidth="1"/>
-    <col min="13" max="13" width="14.7265625" customWidth="1"/>
-    <col min="15" max="15" width="15.36328125" customWidth="1"/>
-    <col min="16" max="16" width="13.453125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="16.5"/>
+    <col customWidth="1" min="6" max="6" width="39.38"/>
+    <col customWidth="1" min="7" max="7" width="32.63"/>
+    <col customWidth="1" min="8" max="8" width="14.63"/>
+    <col customWidth="1" min="9" max="9" width="16.25"/>
+    <col customWidth="1" min="10" max="10" width="117.75"/>
+    <col customWidth="1" min="13" max="13" width="19.75"/>
+    <col customWidth="1" min="15" max="15" width="15.38"/>
+    <col customWidth="1" min="16" max="16" width="13.5"/>
+    <col customWidth="1" min="23" max="23" width="83.25"/>
+    <col customWidth="1" min="25" max="25" width="23.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,16 +504,16 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -467,40 +561,264 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="7"/>
+    <row r="2">
+      <c r="A2" s="3">
+        <v>46160.35866168981</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="5">
+        <v>44638.0</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="5">
+        <v>44669.0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>44669.0</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>44659.0</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="4">
+        <v>2022.0</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="C3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="Q3" s="6"/>
+    <row r="3">
+      <c r="A3" s="3">
+        <v>46160.36209401621</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46160.0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="5">
+        <v>46163.0</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46163.0</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>46163.0</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>46160.41428997685</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" s="7">
+        <v>2026.0</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3"/>
+      <c r="C5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3"/>
+      <c r="C6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="Q6" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="F2"/>
+    <hyperlink r:id="rId2" ref="J2"/>
+    <hyperlink r:id="rId3" ref="L2"/>
+    <hyperlink r:id="rId4" ref="W2"/>
+    <hyperlink r:id="rId5" ref="F3"/>
+    <hyperlink r:id="rId6" ref="J3"/>
+    <hyperlink r:id="rId7" ref="L3"/>
+  </hyperlinks>
+  <drawing r:id="rId8"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="234.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="19.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>